--- a/Philadelphia_76ers_2025-26_stats.xlsx
+++ b/Philadelphia_76ers_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1186,6 +1186,66 @@
       </c>
       <c r="R12" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>31</v>
+      </c>
+      <c r="D13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>13</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>10</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1199,7 +1259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1951,6 +2011,66 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1965,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2718,6 +2838,66 @@
       </c>
       <c r="R12" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2731,7 +2911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3484,6 +3664,66 @@
       </c>
       <c r="R12" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3519,7 +3759,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32.09090909090909</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -3539,7 +3779,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="5">
@@ -3549,7 +3789,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.27272727272727</v>
+        <v>16.58333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -3559,7 +3799,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.36363636363636</v>
+        <v>15.58333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -3569,27 +3809,27 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Andre Drummond</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.6</v>
+        <v>8.333333333333334</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Andre Drummond</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -3599,7 +3839,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="11">
@@ -3609,7 +3849,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.272727272727273</v>
+        <v>3.166666666666667</v>
       </c>
     </row>
     <row r="12">
@@ -3639,7 +3879,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.181818181818182</v>
+        <v>2.166666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -3705,7 +3945,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.272727272727273</v>
+        <v>7.833333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -3715,7 +3955,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.363636363636363</v>
+        <v>4.416666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -3725,7 +3965,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.272727272727272</v>
+        <v>4.166666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -3735,7 +3975,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3.666666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -3755,7 +3995,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.5</v>
+        <v>2.666666666666667</v>
       </c>
     </row>
     <row r="8">
@@ -3765,7 +4005,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.363636363636364</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -3795,7 +4035,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="12">
@@ -3805,7 +4045,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="13">
@@ -3825,7 +4065,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4166666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -3855,7 +4095,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -3891,7 +4131,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.6</v>
+        <v>8.818181818181818</v>
       </c>
     </row>
     <row r="3">
@@ -3901,7 +4141,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -3911,7 +4151,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.545454545454546</v>
+        <v>5.666666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -3927,31 +4167,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.454545454545454</v>
+        <v>5.083333333333333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Trendon Watford</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.25</v>
+        <v>5.083333333333333</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Trendon Watford</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.909090909090909</v>
+        <v>4.777777777777778</v>
       </c>
     </row>
     <row r="9">
@@ -3961,7 +4201,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.272727272727272</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -3971,7 +4211,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.272727272727273</v>
+        <v>3.416666666666667</v>
       </c>
     </row>
     <row r="11">
@@ -3981,7 +4221,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>3.083333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -3991,7 +4231,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.555555555555556</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="13">
@@ -4077,7 +4317,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>3.833333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -4087,47 +4327,47 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.545454545454545</v>
+        <v>2.416666666666667</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.090909090909091</v>
+        <v>2.083333333333333</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.909090909090909</v>
+        <v>1.916666666666667</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Justin Edwards</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Justin Edwards</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.444444444444444</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="8">
@@ -4153,47 +4393,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Trendon Watford</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.625</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Andre Drummond</t>
+          <t>Trendon Watford</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jabari Walker</t>
+          <t>Andre Drummond</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jared McCain</t>
+          <t>Jabari Walker</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Johni Broome</t>
+          <t>Jared McCain</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -4203,7 +4443,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Johni Broome</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -4241,7 +4481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4502,6 +4742,27 @@
         <v>202</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>105</v>
+      </c>
+      <c r="D13" t="n">
+        <v>114</v>
+      </c>
+      <c r="E13" t="n">
+        <v>219</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
